--- a/output/pdf_financials_xlsx/YAK.H.xlsx
+++ b/output/pdf_financials_xlsx/YAK.H.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.37555</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.847141</v>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.609966</v>
+        <v>-0.765584</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.07489899999999999</v>
@@ -854,25 +854,25 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.026133</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.021847</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005617</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002512</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.006813</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.030948</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1549,25 +1549,25 @@
         <v>-5.763752</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.177966</v>
+        <v>-3.204099</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.815069</v>
+        <v>1.793222</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.315654</v>
+        <v>-3.321271</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.625805</v>
+        <v>3.623293</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>16.081911</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10.161451</v>
+        <v>10.154638</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.123516</v>
+        <v>4.092568</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1631,25 +1631,25 @@
         <v>-5.639229</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.096717</v>
+        <v>-3.12285</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.89243</v>
+        <v>1.870583</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.24236</v>
+        <v>-3.247977</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.6946</v>
+        <v>3.692088</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>16.154019</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10.19149</v>
+        <v>10.184677</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.20254</v>
+        <v>4.171592</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1672,25 +1672,25 @@
         <v>-350.2700678150968</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-174.7344324307854</v>
+        <v>-176.2090053164297</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>128.5924836696794</v>
+        <v>127.1079584873839</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-284.2106185847146</v>
+        <v>-284.702979409728</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>396.7504818973062</v>
+        <v>396.4807267924164</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>909.2091510662117</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>321.0898066212964</v>
+        <v>320.8751584341804</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>126.6857866682905</v>
+        <v>125.7528576002007</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -1799,19 +1799,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.881487</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.640771</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.745411</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.737255</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.361771</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>2.396311</v>
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.184825</v>
+        <v>3.066312</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.816624</v>
+        <v>4.457395</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3.946202</v>
+        <v>4.691613</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.737255</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.361771</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>2.396311</v>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.01924</v>
+        <v>0.137753</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.04679</v>
+        <v>0.406019</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.862967</v>
+        <v>0.117556</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.809586</v>
+        <v>5.072331</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12.134944</v>
+        <v>10.773173</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>38.412718</v>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -20746,7 +20746,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -25604,7 +25604,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E307" s="5" t="n">
